--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.71038906796095</v>
+        <v>8.402938223543655</v>
       </c>
       <c r="D2" t="n">
-        <v>42.15767539167297</v>
+        <v>6.850622251146858</v>
       </c>
       <c r="E2" t="n">
-        <v>10.64999568433568</v>
+        <v>1.730624298704548</v>
       </c>
       <c r="F2" t="n">
-        <v>16.59557276766521</v>
+        <v>2.696780574745596</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.15699660848945</v>
+        <v>4.900511948879537</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1598022585063</v>
+        <v>2.300967867007273</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64999568433568</v>
+        <v>1.730624298704548</v>
       </c>
       <c r="F3" t="n">
-        <v>16.59557276766521</v>
+        <v>2.696780574745596</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.66119422143694</v>
+        <v>8.719944060983503</v>
       </c>
       <c r="D4" t="n">
-        <v>53.68221791210375</v>
+        <v>8.723360410716859</v>
       </c>
       <c r="E4" t="n">
-        <v>10.64999568433568</v>
+        <v>1.730624298704548</v>
       </c>
       <c r="F4" t="n">
-        <v>16.59557276766521</v>
+        <v>2.696780574745596</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
